--- a/sources/macro/prices/benchmark-prices.xlsx
+++ b/sources/macro/prices/benchmark-prices.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\dev\cims-models\sources\macro\prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DC6737-9FF9-4267-9C8F-567B2906C8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D389DE6F-1B3D-421F-9EC2-BD4464D4EE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34935" yWindow="3045" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="benchmark-prices" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -426,10 +426,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E829"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +465,7 @@
         <v>Current MeasuresBrent2005</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -482,7 +483,7 @@
         <v>Current MeasuresBrent2006</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -500,7 +501,7 @@
         <v>Current MeasuresBrent2007</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -518,7 +519,7 @@
         <v>Current MeasuresBrent2008</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -536,7 +537,7 @@
         <v>Current MeasuresBrent2009</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -554,7 +555,7 @@
         <v>Current MeasuresBrent2010</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -572,7 +573,7 @@
         <v>Current MeasuresBrent2011</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -590,7 +591,7 @@
         <v>Current MeasuresBrent2012</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -608,7 +609,7 @@
         <v>Current MeasuresBrent2013</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -626,7 +627,7 @@
         <v>Current MeasuresBrent2014</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -644,7 +645,7 @@
         <v>Current MeasuresBrent2015</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -662,7 +663,7 @@
         <v>Current MeasuresBrent2016</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -680,7 +681,7 @@
         <v>Current MeasuresBrent2017</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -698,7 +699,7 @@
         <v>Current MeasuresBrent2018</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -716,7 +717,7 @@
         <v>Current MeasuresBrent2019</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -734,7 +735,7 @@
         <v>Current MeasuresBrent2020</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -752,7 +753,7 @@
         <v>Current MeasuresBrent2021</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -770,7 +771,7 @@
         <v>Current MeasuresBrent2022</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -788,7 +789,7 @@
         <v>Current MeasuresBrent2023</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -806,7 +807,7 @@
         <v>Current MeasuresBrent2024</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -824,7 +825,7 @@
         <v>Current MeasuresBrent2025</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -842,7 +843,7 @@
         <v>Current MeasuresBrent2026</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -860,7 +861,7 @@
         <v>Current MeasuresBrent2027</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -878,7 +879,7 @@
         <v>Current MeasuresBrent2028</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -896,7 +897,7 @@
         <v>Current MeasuresBrent2029</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -914,7 +915,7 @@
         <v>Current MeasuresBrent2030</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -932,7 +933,7 @@
         <v>Current MeasuresBrent2031</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -950,7 +951,7 @@
         <v>Current MeasuresBrent2032</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -968,7 +969,7 @@
         <v>Current MeasuresBrent2033</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -986,7 +987,7 @@
         <v>Current MeasuresBrent2034</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1004,7 +1005,7 @@
         <v>Current MeasuresBrent2035</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1022,7 +1023,7 @@
         <v>Current MeasuresBrent2036</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1040,7 +1041,7 @@
         <v>Current MeasuresBrent2037</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1058,7 +1059,7 @@
         <v>Current MeasuresBrent2038</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1076,7 +1077,7 @@
         <v>Current MeasuresBrent2039</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1094,7 +1095,7 @@
         <v>Current MeasuresBrent2040</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1112,7 +1113,7 @@
         <v>Current MeasuresBrent2041</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -1130,7 +1131,7 @@
         <v>Current MeasuresBrent2042</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -1148,7 +1149,7 @@
         <v>Current MeasuresBrent2043</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -1166,7 +1167,7 @@
         <v>Current MeasuresBrent2044</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>Current MeasuresBrent2045</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -1202,7 +1203,7 @@
         <v>Current MeasuresBrent2046</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -1220,7 +1221,7 @@
         <v>Current MeasuresBrent2047</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -1238,7 +1239,7 @@
         <v>Current MeasuresBrent2048</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1256,7 +1257,7 @@
         <v>Current MeasuresBrent2049</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -1274,7 +1275,7 @@
         <v>Current MeasuresBrent2050</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -1292,7 +1293,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2005</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -1310,7 +1311,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2006</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1328,7 +1329,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2007</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -1346,7 +1347,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2008</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1364,7 +1365,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2009</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -1382,7 +1383,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2010</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1400,7 +1401,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2011</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -1418,7 +1419,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2012</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2013</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -1454,7 +1455,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2014</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -1472,7 +1473,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2015</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -1490,7 +1491,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2016</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -1508,7 +1509,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2017</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -1526,7 +1527,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2018</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -1544,7 +1545,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2019</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -1562,7 +1563,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2020</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -1580,7 +1581,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2021</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -1598,7 +1599,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2022</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -1616,7 +1617,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2023</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -1634,7 +1635,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2024</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -1652,7 +1653,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2025</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -1670,7 +1671,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2026</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -1688,7 +1689,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2027</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2028</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -1724,7 +1725,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2029</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -1742,7 +1743,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2030</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -1760,7 +1761,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2031</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -1778,7 +1779,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2032</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -1796,7 +1797,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2033</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -1814,7 +1815,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2034</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -1832,7 +1833,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2035</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -1850,7 +1851,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2036</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -1868,7 +1869,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2037</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -1886,7 +1887,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2038</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -1904,7 +1905,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2039</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -1922,7 +1923,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2040</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -1940,7 +1941,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2041</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -1958,7 +1959,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2042</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2043</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -1994,7 +1995,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2044</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -2012,7 +2013,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2045</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -2030,7 +2031,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2046</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -2048,7 +2049,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2047</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2048</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -2084,7 +2085,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2049</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>Current MeasuresCanadian Light Sweet (CLS)2050</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -2120,7 +2121,7 @@
         <v>Current MeasuresHenry Hub2005</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -2138,7 +2139,7 @@
         <v>Current MeasuresHenry Hub2006</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -2156,7 +2157,7 @@
         <v>Current MeasuresHenry Hub2007</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -2174,7 +2175,7 @@
         <v>Current MeasuresHenry Hub2008</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -2192,7 +2193,7 @@
         <v>Current MeasuresHenry Hub2009</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -2210,7 +2211,7 @@
         <v>Current MeasuresHenry Hub2010</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -2228,7 +2229,7 @@
         <v>Current MeasuresHenry Hub2011</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -2246,7 +2247,7 @@
         <v>Current MeasuresHenry Hub2012</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -2264,7 +2265,7 @@
         <v>Current MeasuresHenry Hub2013</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -2282,7 +2283,7 @@
         <v>Current MeasuresHenry Hub2014</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -2300,7 +2301,7 @@
         <v>Current MeasuresHenry Hub2015</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -2318,7 +2319,7 @@
         <v>Current MeasuresHenry Hub2016</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -2336,7 +2337,7 @@
         <v>Current MeasuresHenry Hub2017</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -2354,7 +2355,7 @@
         <v>Current MeasuresHenry Hub2018</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -2372,7 +2373,7 @@
         <v>Current MeasuresHenry Hub2019</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -2390,7 +2391,7 @@
         <v>Current MeasuresHenry Hub2020</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -2408,7 +2409,7 @@
         <v>Current MeasuresHenry Hub2021</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -2426,7 +2427,7 @@
         <v>Current MeasuresHenry Hub2022</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -2444,7 +2445,7 @@
         <v>Current MeasuresHenry Hub2023</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -2462,7 +2463,7 @@
         <v>Current MeasuresHenry Hub2024</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -2480,7 +2481,7 @@
         <v>Current MeasuresHenry Hub2025</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -2498,7 +2499,7 @@
         <v>Current MeasuresHenry Hub2026</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>Current MeasuresHenry Hub2027</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -2534,7 +2535,7 @@
         <v>Current MeasuresHenry Hub2028</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -2552,7 +2553,7 @@
         <v>Current MeasuresHenry Hub2029</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -2570,7 +2571,7 @@
         <v>Current MeasuresHenry Hub2030</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -2588,7 +2589,7 @@
         <v>Current MeasuresHenry Hub2031</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -2606,7 +2607,7 @@
         <v>Current MeasuresHenry Hub2032</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>Current MeasuresHenry Hub2033</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -2642,7 +2643,7 @@
         <v>Current MeasuresHenry Hub2034</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -2660,7 +2661,7 @@
         <v>Current MeasuresHenry Hub2035</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -2678,7 +2679,7 @@
         <v>Current MeasuresHenry Hub2036</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -2696,7 +2697,7 @@
         <v>Current MeasuresHenry Hub2037</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -2714,7 +2715,7 @@
         <v>Current MeasuresHenry Hub2038</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -2732,7 +2733,7 @@
         <v>Current MeasuresHenry Hub2039</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -2750,7 +2751,7 @@
         <v>Current MeasuresHenry Hub2040</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -2768,7 +2769,7 @@
         <v>Current MeasuresHenry Hub2041</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -2786,7 +2787,7 @@
         <v>Current MeasuresHenry Hub2042</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -2804,7 +2805,7 @@
         <v>Current MeasuresHenry Hub2043</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -2822,7 +2823,7 @@
         <v>Current MeasuresHenry Hub2044</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -2840,7 +2841,7 @@
         <v>Current MeasuresHenry Hub2045</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -2858,7 +2859,7 @@
         <v>Current MeasuresHenry Hub2046</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -2876,7 +2877,7 @@
         <v>Current MeasuresHenry Hub2047</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -2894,7 +2895,7 @@
         <v>Current MeasuresHenry Hub2048</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -2912,7 +2913,7 @@
         <v>Current MeasuresHenry Hub2049</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -2930,7 +2931,7 @@
         <v>Current MeasuresHenry Hub2050</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -2948,7 +2949,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2005</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>5</v>
       </c>
@@ -2966,7 +2967,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2006</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -2984,7 +2985,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2007</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>5</v>
       </c>
@@ -3002,7 +3003,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2008</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>5</v>
       </c>
@@ -3020,7 +3021,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2009</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>5</v>
       </c>
@@ -3038,7 +3039,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2010</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>5</v>
       </c>
@@ -3056,7 +3057,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2011</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -3074,7 +3075,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2012</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -3092,7 +3093,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2013</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -3110,7 +3111,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2014</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -3128,7 +3129,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2015</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>5</v>
       </c>
@@ -3146,7 +3147,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2016</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -3164,7 +3165,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2017</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -3182,7 +3183,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2018</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -3200,7 +3201,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2019</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -3218,7 +3219,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2020</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -3236,7 +3237,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2021</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -3254,7 +3255,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2022</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -3272,7 +3273,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2023</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>5</v>
       </c>
@@ -3290,7 +3291,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2024</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -3308,7 +3309,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2025</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>5</v>
       </c>
@@ -3326,7 +3327,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2026</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -3344,7 +3345,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2027</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -3362,7 +3363,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2028</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>5</v>
       </c>
@@ -3380,7 +3381,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2029</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -3398,7 +3399,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2030</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>5</v>
       </c>
@@ -3416,7 +3417,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2031</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>5</v>
       </c>
@@ -3434,7 +3435,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2032</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>5</v>
       </c>
@@ -3452,7 +3453,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2033</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>5</v>
       </c>
@@ -3470,7 +3471,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2034</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -3488,7 +3489,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2035</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>5</v>
       </c>
@@ -3506,7 +3507,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2036</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>5</v>
       </c>
@@ -3524,7 +3525,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2037</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>5</v>
       </c>
@@ -3542,7 +3543,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2038</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -3560,7 +3561,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2039</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -3578,7 +3579,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2040</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>5</v>
       </c>
@@ -3596,7 +3597,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2041</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>5</v>
       </c>
@@ -3614,7 +3615,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2042</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -3632,7 +3633,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2043</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>5</v>
       </c>
@@ -3650,7 +3651,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2044</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>5</v>
       </c>
@@ -3668,7 +3669,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2045</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>5</v>
       </c>
@@ -3686,7 +3687,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2046</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>5</v>
       </c>
@@ -3704,7 +3705,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2047</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -3722,7 +3723,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2048</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>5</v>
       </c>
@@ -3740,7 +3741,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2049</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>5</v>
       </c>
@@ -3758,7 +3759,7 @@
         <v>Current MeasuresNova Inventory Transfer (NIT)2050</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>5</v>
       </c>
@@ -3776,7 +3777,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2005</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>5</v>
       </c>
@@ -3794,7 +3795,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2006</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>5</v>
       </c>
@@ -3812,7 +3813,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2007</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>5</v>
       </c>
@@ -3830,7 +3831,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2008</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -3848,7 +3849,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2009</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>5</v>
       </c>
@@ -3866,7 +3867,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2010</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -3884,7 +3885,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2011</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>5</v>
       </c>
@@ -3902,7 +3903,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2012</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -3920,7 +3921,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2013</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>5</v>
       </c>
@@ -3938,7 +3939,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2014</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>5</v>
       </c>
@@ -3956,7 +3957,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2015</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>5</v>
       </c>
@@ -3974,7 +3975,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2016</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>5</v>
       </c>
@@ -3992,7 +3993,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2017</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>5</v>
       </c>
@@ -4010,7 +4011,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2018</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>5</v>
       </c>
@@ -4028,7 +4029,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2019</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -4046,7 +4047,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2020</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>5</v>
       </c>
@@ -4064,7 +4065,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2021</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>5</v>
       </c>
@@ -4082,7 +4083,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2022</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -4100,7 +4101,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2023</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>5</v>
       </c>
@@ -4118,7 +4119,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2024</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>5</v>
       </c>
@@ -4136,7 +4137,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2025</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>5</v>
       </c>
@@ -4154,7 +4155,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2026</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>5</v>
       </c>
@@ -4172,7 +4173,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2027</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>5</v>
       </c>
@@ -4190,7 +4191,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2028</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>5</v>
       </c>
@@ -4208,7 +4209,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2029</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -4226,7 +4227,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2030</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>5</v>
       </c>
@@ -4244,7 +4245,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2031</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>5</v>
       </c>
@@ -4262,7 +4263,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2032</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>5</v>
       </c>
@@ -4280,7 +4281,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2033</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>5</v>
       </c>
@@ -4298,7 +4299,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2034</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>5</v>
       </c>
@@ -4316,7 +4317,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2035</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>5</v>
       </c>
@@ -4334,7 +4335,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2036</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>5</v>
       </c>
@@ -4352,7 +4353,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2037</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -4370,7 +4371,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2038</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>5</v>
       </c>
@@ -4388,7 +4389,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2039</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -4406,7 +4407,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2040</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>5</v>
       </c>
@@ -4424,7 +4425,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2041</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>5</v>
       </c>
@@ -4442,7 +4443,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2042</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -4460,7 +4461,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2043</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>5</v>
       </c>
@@ -4478,7 +4479,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2044</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>5</v>
       </c>
@@ -4496,7 +4497,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2045</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -4514,7 +4515,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2046</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -4532,7 +4533,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2047</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>5</v>
       </c>
@@ -4550,7 +4551,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2048</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>5</v>
       </c>
@@ -4568,7 +4569,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2049</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>5</v>
       </c>
@@ -4586,7 +4587,7 @@
         <v>Current MeasuresWest Texas Intermediate (WTI)2050</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>5</v>
       </c>
@@ -4604,7 +4605,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2005</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>5</v>
       </c>
@@ -4622,7 +4623,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2006</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>5</v>
       </c>
@@ -4640,7 +4641,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2007</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>5</v>
       </c>
@@ -4658,7 +4659,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2008</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>5</v>
       </c>
@@ -4676,7 +4677,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2009</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -4694,7 +4695,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2010</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>5</v>
       </c>
@@ -4712,7 +4713,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2011</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -4730,7 +4731,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2012</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>5</v>
       </c>
@@ -4748,7 +4749,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2013</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>5</v>
       </c>
@@ -4766,7 +4767,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2014</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>5</v>
       </c>
@@ -4784,7 +4785,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2015</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>5</v>
       </c>
@@ -4802,7 +4803,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2016</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>5</v>
       </c>
@@ -4820,7 +4821,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2017</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>5</v>
       </c>
@@ -4838,7 +4839,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2018</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -4856,7 +4857,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2019</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>5</v>
       </c>
@@ -4874,7 +4875,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2020</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>5</v>
       </c>
@@ -4892,7 +4893,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2021</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>5</v>
       </c>
@@ -4910,7 +4911,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2022</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>5</v>
       </c>
@@ -4928,7 +4929,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2023</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>5</v>
       </c>
@@ -4946,7 +4947,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2024</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>5</v>
       </c>
@@ -4964,7 +4965,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2025</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>5</v>
       </c>
@@ -4982,7 +4983,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2026</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>5</v>
       </c>
@@ -5000,7 +5001,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2027</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -5018,7 +5019,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2028</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>5</v>
       </c>
@@ -5036,7 +5037,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2029</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>5</v>
       </c>
@@ -5054,7 +5055,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2030</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>5</v>
       </c>
@@ -5072,7 +5073,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2031</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>5</v>
       </c>
@@ -5090,7 +5091,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2032</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>5</v>
       </c>
@@ -5108,7 +5109,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2033</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>5</v>
       </c>
@@ -5126,7 +5127,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2034</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>5</v>
       </c>
@@ -5144,7 +5145,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2035</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>5</v>
       </c>
@@ -5162,7 +5163,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2036</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -5180,7 +5181,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2037</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>5</v>
       </c>
@@ -5198,7 +5199,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2038</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>5</v>
       </c>
@@ -5216,7 +5217,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2039</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>5</v>
       </c>
@@ -5234,7 +5235,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2040</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>5</v>
       </c>
@@ -5252,7 +5253,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2041</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>5</v>
       </c>
@@ -5270,7 +5271,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2042</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>5</v>
       </c>
@@ -5288,7 +5289,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2043</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>5</v>
       </c>
@@ -5306,7 +5307,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2044</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>5</v>
       </c>
@@ -5324,7 +5325,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2045</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -5342,7 +5343,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2046</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>5</v>
       </c>
@@ -5360,7 +5361,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2047</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>5</v>
       </c>
@@ -5378,7 +5379,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2048</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>5</v>
       </c>
@@ -5396,7 +5397,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2049</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>5</v>
       </c>
@@ -5414,7 +5415,7 @@
         <v>Current MeasuresWestern Canadian Select (WCS)2050</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>12</v>
       </c>
@@ -5432,7 +5433,7 @@
         <v>Canada Net-zeroBrent2005</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>12</v>
       </c>
@@ -5450,7 +5451,7 @@
         <v>Canada Net-zeroBrent2006</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>12</v>
       </c>
@@ -5468,7 +5469,7 @@
         <v>Canada Net-zeroBrent2007</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>12</v>
       </c>
@@ -5486,7 +5487,7 @@
         <v>Canada Net-zeroBrent2008</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>12</v>
       </c>
@@ -5504,7 +5505,7 @@
         <v>Canada Net-zeroBrent2009</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>12</v>
       </c>
@@ -5522,7 +5523,7 @@
         <v>Canada Net-zeroBrent2010</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>12</v>
       </c>
@@ -5540,7 +5541,7 @@
         <v>Canada Net-zeroBrent2011</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>12</v>
       </c>
@@ -5558,7 +5559,7 @@
         <v>Canada Net-zeroBrent2012</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>12</v>
       </c>
@@ -5576,7 +5577,7 @@
         <v>Canada Net-zeroBrent2013</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>12</v>
       </c>
@@ -5594,7 +5595,7 @@
         <v>Canada Net-zeroBrent2014</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>12</v>
       </c>
@@ -5612,7 +5613,7 @@
         <v>Canada Net-zeroBrent2015</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>12</v>
       </c>
@@ -5630,7 +5631,7 @@
         <v>Canada Net-zeroBrent2016</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>12</v>
       </c>
@@ -5648,7 +5649,7 @@
         <v>Canada Net-zeroBrent2017</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>12</v>
       </c>
@@ -5666,7 +5667,7 @@
         <v>Canada Net-zeroBrent2018</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>12</v>
       </c>
@@ -5684,7 +5685,7 @@
         <v>Canada Net-zeroBrent2019</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>12</v>
       </c>
@@ -5702,7 +5703,7 @@
         <v>Canada Net-zeroBrent2020</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>12</v>
       </c>
@@ -5720,7 +5721,7 @@
         <v>Canada Net-zeroBrent2021</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>12</v>
       </c>
@@ -5738,7 +5739,7 @@
         <v>Canada Net-zeroBrent2022</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>12</v>
       </c>
@@ -5756,7 +5757,7 @@
         <v>Canada Net-zeroBrent2023</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>12</v>
       </c>
@@ -5774,7 +5775,7 @@
         <v>Canada Net-zeroBrent2024</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>12</v>
       </c>
@@ -5792,7 +5793,7 @@
         <v>Canada Net-zeroBrent2025</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>12</v>
       </c>
@@ -5810,7 +5811,7 @@
         <v>Canada Net-zeroBrent2026</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>12</v>
       </c>
@@ -5828,7 +5829,7 @@
         <v>Canada Net-zeroBrent2027</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>12</v>
       </c>
@@ -5846,7 +5847,7 @@
         <v>Canada Net-zeroBrent2028</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>12</v>
       </c>
@@ -5864,7 +5865,7 @@
         <v>Canada Net-zeroBrent2029</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>12</v>
       </c>
@@ -5882,7 +5883,7 @@
         <v>Canada Net-zeroBrent2030</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>12</v>
       </c>
@@ -5900,7 +5901,7 @@
         <v>Canada Net-zeroBrent2031</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>12</v>
       </c>
@@ -5918,7 +5919,7 @@
         <v>Canada Net-zeroBrent2032</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>12</v>
       </c>
@@ -5936,7 +5937,7 @@
         <v>Canada Net-zeroBrent2033</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>12</v>
       </c>
@@ -5954,7 +5955,7 @@
         <v>Canada Net-zeroBrent2034</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>12</v>
       </c>
@@ -5972,7 +5973,7 @@
         <v>Canada Net-zeroBrent2035</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>12</v>
       </c>
@@ -5990,7 +5991,7 @@
         <v>Canada Net-zeroBrent2036</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>12</v>
       </c>
@@ -6008,7 +6009,7 @@
         <v>Canada Net-zeroBrent2037</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>12</v>
       </c>
@@ -6026,7 +6027,7 @@
         <v>Canada Net-zeroBrent2038</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>12</v>
       </c>
@@ -6044,7 +6045,7 @@
         <v>Canada Net-zeroBrent2039</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>12</v>
       </c>
@@ -6062,7 +6063,7 @@
         <v>Canada Net-zeroBrent2040</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>12</v>
       </c>
@@ -6080,7 +6081,7 @@
         <v>Canada Net-zeroBrent2041</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>12</v>
       </c>
@@ -6098,7 +6099,7 @@
         <v>Canada Net-zeroBrent2042</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>12</v>
       </c>
@@ -6116,7 +6117,7 @@
         <v>Canada Net-zeroBrent2043</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>12</v>
       </c>
@@ -6134,7 +6135,7 @@
         <v>Canada Net-zeroBrent2044</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>12</v>
       </c>
@@ -6152,7 +6153,7 @@
         <v>Canada Net-zeroBrent2045</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>12</v>
       </c>
@@ -6170,7 +6171,7 @@
         <v>Canada Net-zeroBrent2046</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>12</v>
       </c>
@@ -6188,7 +6189,7 @@
         <v>Canada Net-zeroBrent2047</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>12</v>
       </c>
@@ -6206,7 +6207,7 @@
         <v>Canada Net-zeroBrent2048</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>12</v>
       </c>
@@ -6224,7 +6225,7 @@
         <v>Canada Net-zeroBrent2049</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>12</v>
       </c>
@@ -6242,7 +6243,7 @@
         <v>Canada Net-zeroBrent2050</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>12</v>
       </c>
@@ -6260,7 +6261,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2005</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>12</v>
       </c>
@@ -6278,7 +6279,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2006</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>12</v>
       </c>
@@ -6296,7 +6297,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2007</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>12</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2008</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>12</v>
       </c>
@@ -6332,7 +6333,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2009</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>12</v>
       </c>
@@ -6350,7 +6351,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2010</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>12</v>
       </c>
@@ -6368,7 +6369,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2011</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>12</v>
       </c>
@@ -6386,7 +6387,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2012</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>12</v>
       </c>
@@ -6404,7 +6405,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2013</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>12</v>
       </c>
@@ -6422,7 +6423,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2014</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>12</v>
       </c>
@@ -6440,7 +6441,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2015</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>12</v>
       </c>
@@ -6458,7 +6459,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2016</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>12</v>
       </c>
@@ -6476,7 +6477,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2017</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>12</v>
       </c>
@@ -6494,7 +6495,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2018</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>12</v>
       </c>
@@ -6512,7 +6513,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2019</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>12</v>
       </c>
@@ -6530,7 +6531,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2020</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>12</v>
       </c>
@@ -6548,7 +6549,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2021</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>12</v>
       </c>
@@ -6566,7 +6567,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2022</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>12</v>
       </c>
@@ -6584,7 +6585,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2023</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>12</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2024</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>12</v>
       </c>
@@ -6620,7 +6621,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2025</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>12</v>
       </c>
@@ -6638,7 +6639,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2026</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>12</v>
       </c>
@@ -6656,7 +6657,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2027</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>12</v>
       </c>
@@ -6674,7 +6675,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2028</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>12</v>
       </c>
@@ -6692,7 +6693,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2029</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>12</v>
       </c>
@@ -6710,7 +6711,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2030</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>12</v>
       </c>
@@ -6728,7 +6729,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2031</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>12</v>
       </c>
@@ -6746,7 +6747,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2032</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>12</v>
       </c>
@@ -6764,7 +6765,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2033</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>12</v>
       </c>
@@ -6782,7 +6783,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2034</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>12</v>
       </c>
@@ -6800,7 +6801,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2035</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>12</v>
       </c>
@@ -6818,7 +6819,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2036</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>12</v>
       </c>
@@ -6836,7 +6837,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2037</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>12</v>
       </c>
@@ -6854,7 +6855,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2038</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>12</v>
       </c>
@@ -6872,7 +6873,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2039</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>12</v>
       </c>
@@ -6890,7 +6891,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2040</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>12</v>
       </c>
@@ -6908,7 +6909,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2041</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>12</v>
       </c>
@@ -6926,7 +6927,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2042</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>12</v>
       </c>
@@ -6944,7 +6945,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2043</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>12</v>
       </c>
@@ -6962,7 +6963,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2044</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>12</v>
       </c>
@@ -6980,7 +6981,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2045</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>12</v>
       </c>
@@ -6998,7 +6999,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2046</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>12</v>
       </c>
@@ -7016,7 +7017,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2047</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>12</v>
       </c>
@@ -7034,7 +7035,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2048</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>12</v>
       </c>
@@ -7052,7 +7053,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2049</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>12</v>
       </c>
@@ -7070,7 +7071,7 @@
         <v>Canada Net-zeroCanadian Light Sweet (CLS)2050</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>12</v>
       </c>
@@ -7088,7 +7089,7 @@
         <v>Canada Net-zeroHenry Hub2005</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>12</v>
       </c>
@@ -7106,7 +7107,7 @@
         <v>Canada Net-zeroHenry Hub2006</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>12</v>
       </c>
@@ -7124,7 +7125,7 @@
         <v>Canada Net-zeroHenry Hub2007</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>12</v>
       </c>
@@ -7142,7 +7143,7 @@
         <v>Canada Net-zeroHenry Hub2008</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>12</v>
       </c>
@@ -7160,7 +7161,7 @@
         <v>Canada Net-zeroHenry Hub2009</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>12</v>
       </c>
@@ -7178,7 +7179,7 @@
         <v>Canada Net-zeroHenry Hub2010</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>12</v>
       </c>
@@ -7196,7 +7197,7 @@
         <v>Canada Net-zeroHenry Hub2011</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>12</v>
       </c>
@@ -7214,7 +7215,7 @@
         <v>Canada Net-zeroHenry Hub2012</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>12</v>
       </c>
@@ -7232,7 +7233,7 @@
         <v>Canada Net-zeroHenry Hub2013</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>12</v>
       </c>
@@ -7250,7 +7251,7 @@
         <v>Canada Net-zeroHenry Hub2014</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>12</v>
       </c>
@@ -7268,7 +7269,7 @@
         <v>Canada Net-zeroHenry Hub2015</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>12</v>
       </c>
@@ -7286,7 +7287,7 @@
         <v>Canada Net-zeroHenry Hub2016</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>12</v>
       </c>
@@ -7304,7 +7305,7 @@
         <v>Canada Net-zeroHenry Hub2017</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>12</v>
       </c>
@@ -7322,7 +7323,7 @@
         <v>Canada Net-zeroHenry Hub2018</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>12</v>
       </c>
@@ -7340,7 +7341,7 @@
         <v>Canada Net-zeroHenry Hub2019</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>12</v>
       </c>
@@ -7358,7 +7359,7 @@
         <v>Canada Net-zeroHenry Hub2020</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>12</v>
       </c>
@@ -7376,7 +7377,7 @@
         <v>Canada Net-zeroHenry Hub2021</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>12</v>
       </c>
@@ -7394,7 +7395,7 @@
         <v>Canada Net-zeroHenry Hub2022</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>12</v>
       </c>
@@ -7412,7 +7413,7 @@
         <v>Canada Net-zeroHenry Hub2023</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>12</v>
       </c>
@@ -7430,7 +7431,7 @@
         <v>Canada Net-zeroHenry Hub2024</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>12</v>
       </c>
@@ -7448,7 +7449,7 @@
         <v>Canada Net-zeroHenry Hub2025</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>12</v>
       </c>
@@ -7466,7 +7467,7 @@
         <v>Canada Net-zeroHenry Hub2026</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>12</v>
       </c>
@@ -7484,7 +7485,7 @@
         <v>Canada Net-zeroHenry Hub2027</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>12</v>
       </c>
@@ -7502,7 +7503,7 @@
         <v>Canada Net-zeroHenry Hub2028</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>12</v>
       </c>
@@ -7520,7 +7521,7 @@
         <v>Canada Net-zeroHenry Hub2029</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>12</v>
       </c>
@@ -7538,7 +7539,7 @@
         <v>Canada Net-zeroHenry Hub2030</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>12</v>
       </c>
@@ -7556,7 +7557,7 @@
         <v>Canada Net-zeroHenry Hub2031</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>12</v>
       </c>
@@ -7574,7 +7575,7 @@
         <v>Canada Net-zeroHenry Hub2032</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>12</v>
       </c>
@@ -7592,7 +7593,7 @@
         <v>Canada Net-zeroHenry Hub2033</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>12</v>
       </c>
@@ -7610,7 +7611,7 @@
         <v>Canada Net-zeroHenry Hub2034</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>12</v>
       </c>
@@ -7628,7 +7629,7 @@
         <v>Canada Net-zeroHenry Hub2035</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>12</v>
       </c>
@@ -7646,7 +7647,7 @@
         <v>Canada Net-zeroHenry Hub2036</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>12</v>
       </c>
@@ -7664,7 +7665,7 @@
         <v>Canada Net-zeroHenry Hub2037</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>12</v>
       </c>
@@ -7682,7 +7683,7 @@
         <v>Canada Net-zeroHenry Hub2038</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>12</v>
       </c>
@@ -7700,7 +7701,7 @@
         <v>Canada Net-zeroHenry Hub2039</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>12</v>
       </c>
@@ -7718,7 +7719,7 @@
         <v>Canada Net-zeroHenry Hub2040</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>12</v>
       </c>
@@ -7736,7 +7737,7 @@
         <v>Canada Net-zeroHenry Hub2041</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>12</v>
       </c>
@@ -7754,7 +7755,7 @@
         <v>Canada Net-zeroHenry Hub2042</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>12</v>
       </c>
@@ -7772,7 +7773,7 @@
         <v>Canada Net-zeroHenry Hub2043</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>12</v>
       </c>
@@ -7790,7 +7791,7 @@
         <v>Canada Net-zeroHenry Hub2044</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>12</v>
       </c>
@@ -7808,7 +7809,7 @@
         <v>Canada Net-zeroHenry Hub2045</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>12</v>
       </c>
@@ -7826,7 +7827,7 @@
         <v>Canada Net-zeroHenry Hub2046</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>12</v>
       </c>
@@ -7844,7 +7845,7 @@
         <v>Canada Net-zeroHenry Hub2047</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>12</v>
       </c>
@@ -7862,7 +7863,7 @@
         <v>Canada Net-zeroHenry Hub2048</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>12</v>
       </c>
@@ -7880,7 +7881,7 @@
         <v>Canada Net-zeroHenry Hub2049</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>12</v>
       </c>
@@ -7898,7 +7899,7 @@
         <v>Canada Net-zeroHenry Hub2050</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>12</v>
       </c>
@@ -7916,7 +7917,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2005</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>12</v>
       </c>
@@ -7934,7 +7935,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2006</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>12</v>
       </c>
@@ -7952,7 +7953,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2007</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>12</v>
       </c>
@@ -7970,7 +7971,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2008</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>12</v>
       </c>
@@ -7988,7 +7989,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2009</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>12</v>
       </c>
@@ -8006,7 +8007,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2010</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>12</v>
       </c>
@@ -8024,7 +8025,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2011</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>12</v>
       </c>
@@ -8042,7 +8043,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2012</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>12</v>
       </c>
@@ -8060,7 +8061,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2013</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>12</v>
       </c>
@@ -8078,7 +8079,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2014</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>12</v>
       </c>
@@ -8096,7 +8097,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2015</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>12</v>
       </c>
@@ -8114,7 +8115,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2016</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>12</v>
       </c>
@@ -8132,7 +8133,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2017</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>12</v>
       </c>
@@ -8150,7 +8151,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2018</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>12</v>
       </c>
@@ -8168,7 +8169,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2019</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>12</v>
       </c>
@@ -8186,7 +8187,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2020</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>12</v>
       </c>
@@ -8204,7 +8205,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2021</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>12</v>
       </c>
@@ -8222,7 +8223,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2022</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>12</v>
       </c>
@@ -8240,7 +8241,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2023</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>12</v>
       </c>
@@ -8258,7 +8259,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2024</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>12</v>
       </c>
@@ -8276,7 +8277,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2025</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>12</v>
       </c>
@@ -8294,7 +8295,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2026</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>12</v>
       </c>
@@ -8312,7 +8313,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2027</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>12</v>
       </c>
@@ -8330,7 +8331,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2028</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>12</v>
       </c>
@@ -8348,7 +8349,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2029</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>12</v>
       </c>
@@ -8366,7 +8367,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2030</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>12</v>
       </c>
@@ -8384,7 +8385,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2031</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>12</v>
       </c>
@@ -8402,7 +8403,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2032</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>12</v>
       </c>
@@ -8420,7 +8421,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2033</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>12</v>
       </c>
@@ -8438,7 +8439,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2034</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>12</v>
       </c>
@@ -8456,7 +8457,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2035</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>12</v>
       </c>
@@ -8474,7 +8475,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2036</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>12</v>
       </c>
@@ -8492,7 +8493,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2037</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>12</v>
       </c>
@@ -8510,7 +8511,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2038</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>12</v>
       </c>
@@ -8528,7 +8529,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2039</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>12</v>
       </c>
@@ -8546,7 +8547,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2040</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>12</v>
       </c>
@@ -8564,7 +8565,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2041</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>12</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2042</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>12</v>
       </c>
@@ -8600,7 +8601,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2043</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>12</v>
       </c>
@@ -8618,7 +8619,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2044</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>12</v>
       </c>
@@ -8636,7 +8637,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2045</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>12</v>
       </c>
@@ -8654,7 +8655,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2046</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>12</v>
       </c>
@@ -8672,7 +8673,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2047</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>12</v>
       </c>
@@ -8690,7 +8691,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2048</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>12</v>
       </c>
@@ -8708,7 +8709,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2049</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>12</v>
       </c>
@@ -8726,7 +8727,7 @@
         <v>Canada Net-zeroNova Inventory Transfer (NIT)2050</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>12</v>
       </c>
@@ -8744,7 +8745,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2005</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>12</v>
       </c>
@@ -8762,7 +8763,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2006</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>12</v>
       </c>
@@ -8780,7 +8781,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2007</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>12</v>
       </c>
@@ -8798,7 +8799,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2008</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>12</v>
       </c>
@@ -8816,7 +8817,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2009</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>12</v>
       </c>
@@ -8834,7 +8835,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2010</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>12</v>
       </c>
@@ -8852,7 +8853,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2011</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>12</v>
       </c>
@@ -8870,7 +8871,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2012</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>12</v>
       </c>
@@ -8888,7 +8889,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2013</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>12</v>
       </c>
@@ -8906,7 +8907,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2014</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>12</v>
       </c>
@@ -8924,7 +8925,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2015</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>12</v>
       </c>
@@ -8942,7 +8943,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2016</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>12</v>
       </c>
@@ -8960,7 +8961,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2017</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>12</v>
       </c>
@@ -8978,7 +8979,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2018</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>12</v>
       </c>
@@ -8996,7 +8997,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2019</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>12</v>
       </c>
@@ -9014,7 +9015,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2020</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>12</v>
       </c>
@@ -9032,7 +9033,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2021</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>12</v>
       </c>
@@ -9050,7 +9051,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2022</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>12</v>
       </c>
@@ -9068,7 +9069,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2023</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>12</v>
       </c>
@@ -9086,7 +9087,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2024</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>12</v>
       </c>
@@ -9104,7 +9105,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2025</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>12</v>
       </c>
@@ -9122,7 +9123,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2026</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>12</v>
       </c>
@@ -9140,7 +9141,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2027</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>12</v>
       </c>
@@ -9158,7 +9159,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2028</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>12</v>
       </c>
@@ -9176,7 +9177,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2029</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>12</v>
       </c>
@@ -9194,7 +9195,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2030</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>12</v>
       </c>
@@ -9212,7 +9213,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2031</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>12</v>
       </c>
@@ -9230,7 +9231,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2032</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>12</v>
       </c>
@@ -9248,7 +9249,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2033</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>12</v>
       </c>
@@ -9266,7 +9267,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2034</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>12</v>
       </c>
@@ -9284,7 +9285,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2035</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>12</v>
       </c>
@@ -9302,7 +9303,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2036</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>12</v>
       </c>
@@ -9320,7 +9321,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2037</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>12</v>
       </c>
@@ -9338,7 +9339,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2038</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>12</v>
       </c>
@@ -9356,7 +9357,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2039</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>12</v>
       </c>
@@ -9374,7 +9375,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2040</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>12</v>
       </c>
@@ -9392,7 +9393,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2041</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>12</v>
       </c>
@@ -9410,7 +9411,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2042</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>12</v>
       </c>
@@ -9428,7 +9429,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2043</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>12</v>
       </c>
@@ -9446,7 +9447,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2044</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>12</v>
       </c>
@@ -9464,7 +9465,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2045</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>12</v>
       </c>
@@ -9482,7 +9483,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2046</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>12</v>
       </c>
@@ -9500,7 +9501,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2047</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>12</v>
       </c>
@@ -9518,7 +9519,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2048</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>12</v>
       </c>
@@ -9536,7 +9537,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2049</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>12</v>
       </c>
@@ -9554,7 +9555,7 @@
         <v>Canada Net-zeroWest Texas Intermediate (WTI)2050</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>12</v>
       </c>
@@ -9572,7 +9573,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2005</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>12</v>
       </c>
@@ -9590,7 +9591,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2006</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>12</v>
       </c>
@@ -9608,7 +9609,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2007</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>12</v>
       </c>
@@ -9626,7 +9627,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2008</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>12</v>
       </c>
@@ -9644,7 +9645,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2009</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>12</v>
       </c>
@@ -9662,7 +9663,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2010</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>12</v>
       </c>
@@ -9680,7 +9681,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2011</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>12</v>
       </c>
@@ -9698,7 +9699,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2012</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>12</v>
       </c>
@@ -9716,7 +9717,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2013</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>12</v>
       </c>
@@ -9734,7 +9735,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2014</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>12</v>
       </c>
@@ -9752,7 +9753,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2015</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>12</v>
       </c>
@@ -9770,7 +9771,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2016</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>12</v>
       </c>
@@ -9788,7 +9789,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2017</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>12</v>
       </c>
@@ -9806,7 +9807,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2018</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>12</v>
       </c>
@@ -9824,7 +9825,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2019</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>12</v>
       </c>
@@ -9842,7 +9843,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2020</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>12</v>
       </c>
@@ -9860,7 +9861,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2021</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>12</v>
       </c>
@@ -9878,7 +9879,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2022</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>12</v>
       </c>
@@ -9896,7 +9897,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2023</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>12</v>
       </c>
@@ -9914,7 +9915,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2024</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>12</v>
       </c>
@@ -9932,7 +9933,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2025</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>12</v>
       </c>
@@ -9950,7 +9951,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2026</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>12</v>
       </c>
@@ -9968,7 +9969,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2027</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>12</v>
       </c>
@@ -9986,7 +9987,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2028</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>12</v>
       </c>
@@ -10004,7 +10005,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2029</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>12</v>
       </c>
@@ -10022,7 +10023,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2030</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>12</v>
       </c>
@@ -10040,7 +10041,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2031</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>12</v>
       </c>
@@ -10058,7 +10059,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2032</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>12</v>
       </c>
@@ -10076,7 +10077,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2033</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>12</v>
       </c>
@@ -10094,7 +10095,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2034</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>12</v>
       </c>
@@ -10112,7 +10113,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2035</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>12</v>
       </c>
@@ -10130,7 +10131,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2036</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>12</v>
       </c>
@@ -10148,7 +10149,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2037</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>12</v>
       </c>
@@ -10166,7 +10167,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2038</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>12</v>
       </c>
@@ -10184,7 +10185,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2039</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>12</v>
       </c>
@@ -10202,7 +10203,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2040</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>12</v>
       </c>
@@ -10220,7 +10221,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2041</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>12</v>
       </c>
@@ -10238,7 +10239,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2042</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>12</v>
       </c>
@@ -10256,7 +10257,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2043</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>12</v>
       </c>
@@ -10274,7 +10275,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2044</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>12</v>
       </c>
@@ -10292,7 +10293,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2045</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>12</v>
       </c>
@@ -10310,7 +10311,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2046</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>12</v>
       </c>
@@ -10328,7 +10329,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2047</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>12</v>
       </c>
@@ -10346,7 +10347,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2048</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>12</v>
       </c>
@@ -10364,7 +10365,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2049</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>12</v>
       </c>
@@ -10382,7 +10383,7 @@
         <v>Canada Net-zeroWestern Canadian Select (WCS)2050</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>13</v>
       </c>
@@ -10400,7 +10401,7 @@
         <v>Global Net-zeroBrent2005</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>13</v>
       </c>
@@ -10418,7 +10419,7 @@
         <v>Global Net-zeroBrent2006</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>13</v>
       </c>
@@ -10436,7 +10437,7 @@
         <v>Global Net-zeroBrent2007</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>13</v>
       </c>
@@ -10454,7 +10455,7 @@
         <v>Global Net-zeroBrent2008</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>13</v>
       </c>
@@ -10472,7 +10473,7 @@
         <v>Global Net-zeroBrent2009</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>13</v>
       </c>
@@ -10490,7 +10491,7 @@
         <v>Global Net-zeroBrent2010</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>13</v>
       </c>
@@ -10508,7 +10509,7 @@
         <v>Global Net-zeroBrent2011</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>13</v>
       </c>
@@ -10526,7 +10527,7 @@
         <v>Global Net-zeroBrent2012</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>13</v>
       </c>
@@ -10544,7 +10545,7 @@
         <v>Global Net-zeroBrent2013</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>13</v>
       </c>
@@ -10562,7 +10563,7 @@
         <v>Global Net-zeroBrent2014</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>13</v>
       </c>
@@ -10580,7 +10581,7 @@
         <v>Global Net-zeroBrent2015</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>13</v>
       </c>
@@ -10598,7 +10599,7 @@
         <v>Global Net-zeroBrent2016</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>13</v>
       </c>
@@ -10616,7 +10617,7 @@
         <v>Global Net-zeroBrent2017</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>13</v>
       </c>
@@ -10634,7 +10635,7 @@
         <v>Global Net-zeroBrent2018</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>13</v>
       </c>
@@ -10652,7 +10653,7 @@
         <v>Global Net-zeroBrent2019</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>13</v>
       </c>
@@ -10670,7 +10671,7 @@
         <v>Global Net-zeroBrent2020</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>13</v>
       </c>
@@ -10688,7 +10689,7 @@
         <v>Global Net-zeroBrent2021</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>13</v>
       </c>
@@ -10706,7 +10707,7 @@
         <v>Global Net-zeroBrent2022</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>13</v>
       </c>
@@ -10724,7 +10725,7 @@
         <v>Global Net-zeroBrent2023</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>13</v>
       </c>
@@ -10742,7 +10743,7 @@
         <v>Global Net-zeroBrent2024</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>13</v>
       </c>
@@ -10760,7 +10761,7 @@
         <v>Global Net-zeroBrent2025</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>13</v>
       </c>
@@ -10778,7 +10779,7 @@
         <v>Global Net-zeroBrent2026</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>13</v>
       </c>
@@ -10796,7 +10797,7 @@
         <v>Global Net-zeroBrent2027</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>13</v>
       </c>
@@ -10814,7 +10815,7 @@
         <v>Global Net-zeroBrent2028</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>13</v>
       </c>
@@ -10832,7 +10833,7 @@
         <v>Global Net-zeroBrent2029</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>13</v>
       </c>
@@ -10850,7 +10851,7 @@
         <v>Global Net-zeroBrent2030</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>13</v>
       </c>
@@ -10868,7 +10869,7 @@
         <v>Global Net-zeroBrent2031</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>13</v>
       </c>
@@ -10886,7 +10887,7 @@
         <v>Global Net-zeroBrent2032</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>13</v>
       </c>
@@ -10904,7 +10905,7 @@
         <v>Global Net-zeroBrent2033</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>13</v>
       </c>
@@ -10922,7 +10923,7 @@
         <v>Global Net-zeroBrent2034</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>13</v>
       </c>
@@ -10940,7 +10941,7 @@
         <v>Global Net-zeroBrent2035</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>13</v>
       </c>
@@ -10958,7 +10959,7 @@
         <v>Global Net-zeroBrent2036</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>13</v>
       </c>
@@ -10976,7 +10977,7 @@
         <v>Global Net-zeroBrent2037</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>13</v>
       </c>
@@ -10994,7 +10995,7 @@
         <v>Global Net-zeroBrent2038</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>13</v>
       </c>
@@ -11012,7 +11013,7 @@
         <v>Global Net-zeroBrent2039</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>13</v>
       </c>
@@ -11030,7 +11031,7 @@
         <v>Global Net-zeroBrent2040</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>13</v>
       </c>
@@ -11048,7 +11049,7 @@
         <v>Global Net-zeroBrent2041</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>13</v>
       </c>
@@ -11066,7 +11067,7 @@
         <v>Global Net-zeroBrent2042</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>13</v>
       </c>
@@ -11084,7 +11085,7 @@
         <v>Global Net-zeroBrent2043</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>13</v>
       </c>
@@ -11102,7 +11103,7 @@
         <v>Global Net-zeroBrent2044</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>13</v>
       </c>
@@ -11120,7 +11121,7 @@
         <v>Global Net-zeroBrent2045</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>13</v>
       </c>
@@ -11138,7 +11139,7 @@
         <v>Global Net-zeroBrent2046</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>13</v>
       </c>
@@ -11156,7 +11157,7 @@
         <v>Global Net-zeroBrent2047</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>13</v>
       </c>
@@ -11174,7 +11175,7 @@
         <v>Global Net-zeroBrent2048</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>13</v>
       </c>
@@ -11192,7 +11193,7 @@
         <v>Global Net-zeroBrent2049</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>13</v>
       </c>
@@ -11210,7 +11211,7 @@
         <v>Global Net-zeroBrent2050</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>13</v>
       </c>
@@ -11228,7 +11229,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2005</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>13</v>
       </c>
@@ -11246,7 +11247,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2006</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>13</v>
       </c>
@@ -11264,7 +11265,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2007</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>13</v>
       </c>
@@ -11282,7 +11283,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2008</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>13</v>
       </c>
@@ -11300,7 +11301,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2009</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>13</v>
       </c>
@@ -11318,7 +11319,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2010</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>13</v>
       </c>
@@ -11336,7 +11337,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2011</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>13</v>
       </c>
@@ -11354,7 +11355,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2012</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>13</v>
       </c>
@@ -11372,7 +11373,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2013</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>13</v>
       </c>
@@ -11390,7 +11391,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2014</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>13</v>
       </c>
@@ -11408,7 +11409,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2015</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>13</v>
       </c>
@@ -11426,7 +11427,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2016</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>13</v>
       </c>
@@ -11444,7 +11445,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2017</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>13</v>
       </c>
@@ -11462,7 +11463,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2018</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>13</v>
       </c>
@@ -11480,7 +11481,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2019</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>13</v>
       </c>
@@ -11498,7 +11499,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2020</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>13</v>
       </c>
@@ -11516,7 +11517,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2021</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>13</v>
       </c>
@@ -11534,7 +11535,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2022</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>13</v>
       </c>
@@ -11552,7 +11553,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2023</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>13</v>
       </c>
@@ -11570,7 +11571,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2024</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>13</v>
       </c>
@@ -11588,7 +11589,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2025</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>13</v>
       </c>
@@ -11606,7 +11607,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2026</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>13</v>
       </c>
@@ -11624,7 +11625,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2027</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>13</v>
       </c>
@@ -11642,7 +11643,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2028</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>13</v>
       </c>
@@ -11660,7 +11661,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2029</v>
       </c>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>13</v>
       </c>
@@ -11678,7 +11679,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2030</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>13</v>
       </c>
@@ -11696,7 +11697,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2031</v>
       </c>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>13</v>
       </c>
@@ -11714,7 +11715,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2032</v>
       </c>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>13</v>
       </c>
@@ -11732,7 +11733,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2033</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>13</v>
       </c>
@@ -11750,7 +11751,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2034</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>13</v>
       </c>
@@ -11768,7 +11769,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2035</v>
       </c>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>13</v>
       </c>
@@ -11786,7 +11787,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2036</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>13</v>
       </c>
@@ -11804,7 +11805,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2037</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>13</v>
       </c>
@@ -11822,7 +11823,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2038</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>13</v>
       </c>
@@ -11840,7 +11841,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2039</v>
       </c>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>13</v>
       </c>
@@ -11858,7 +11859,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2040</v>
       </c>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>13</v>
       </c>
@@ -11876,7 +11877,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2041</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>13</v>
       </c>
@@ -11894,7 +11895,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2042</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>13</v>
       </c>
@@ -11912,7 +11913,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2043</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>13</v>
       </c>
@@ -11930,7 +11931,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2044</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>13</v>
       </c>
@@ -11948,7 +11949,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2045</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>13</v>
       </c>
@@ -11966,7 +11967,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2046</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>13</v>
       </c>
@@ -11984,7 +11985,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2047</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>13</v>
       </c>
@@ -12002,7 +12003,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2048</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>13</v>
       </c>
@@ -12020,7 +12021,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2049</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>13</v>
       </c>
@@ -12038,7 +12039,7 @@
         <v>Global Net-zeroCanadian Light Sweet (CLS)2050</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>13</v>
       </c>
@@ -12056,7 +12057,7 @@
         <v>Global Net-zeroHenry Hub2005</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>13</v>
       </c>
@@ -12074,7 +12075,7 @@
         <v>Global Net-zeroHenry Hub2006</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>13</v>
       </c>
@@ -12092,7 +12093,7 @@
         <v>Global Net-zeroHenry Hub2007</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>13</v>
       </c>
@@ -12110,7 +12111,7 @@
         <v>Global Net-zeroHenry Hub2008</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>13</v>
       </c>
@@ -12128,7 +12129,7 @@
         <v>Global Net-zeroHenry Hub2009</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>13</v>
       </c>
@@ -12146,7 +12147,7 @@
         <v>Global Net-zeroHenry Hub2010</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>13</v>
       </c>
@@ -12164,7 +12165,7 @@
         <v>Global Net-zeroHenry Hub2011</v>
       </c>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>13</v>
       </c>
@@ -12182,7 +12183,7 @@
         <v>Global Net-zeroHenry Hub2012</v>
       </c>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>13</v>
       </c>
@@ -12200,7 +12201,7 @@
         <v>Global Net-zeroHenry Hub2013</v>
       </c>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>13</v>
       </c>
@@ -12218,7 +12219,7 @@
         <v>Global Net-zeroHenry Hub2014</v>
       </c>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>13</v>
       </c>
@@ -12236,7 +12237,7 @@
         <v>Global Net-zeroHenry Hub2015</v>
       </c>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>13</v>
       </c>
@@ -12254,7 +12255,7 @@
         <v>Global Net-zeroHenry Hub2016</v>
       </c>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>13</v>
       </c>
@@ -12272,7 +12273,7 @@
         <v>Global Net-zeroHenry Hub2017</v>
       </c>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>13</v>
       </c>
@@ -12290,7 +12291,7 @@
         <v>Global Net-zeroHenry Hub2018</v>
       </c>
     </row>
-    <row r="660" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>13</v>
       </c>
@@ -12308,7 +12309,7 @@
         <v>Global Net-zeroHenry Hub2019</v>
       </c>
     </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>13</v>
       </c>
@@ -12326,7 +12327,7 @@
         <v>Global Net-zeroHenry Hub2020</v>
       </c>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>13</v>
       </c>
@@ -12344,7 +12345,7 @@
         <v>Global Net-zeroHenry Hub2021</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>13</v>
       </c>
@@ -12362,7 +12363,7 @@
         <v>Global Net-zeroHenry Hub2022</v>
       </c>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>13</v>
       </c>
@@ -12380,7 +12381,7 @@
         <v>Global Net-zeroHenry Hub2023</v>
       </c>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>13</v>
       </c>
@@ -12398,7 +12399,7 @@
         <v>Global Net-zeroHenry Hub2024</v>
       </c>
     </row>
-    <row r="666" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>13</v>
       </c>
@@ -12416,7 +12417,7 @@
         <v>Global Net-zeroHenry Hub2025</v>
       </c>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>13</v>
       </c>
@@ -12434,7 +12435,7 @@
         <v>Global Net-zeroHenry Hub2026</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>13</v>
       </c>
@@ -12452,7 +12453,7 @@
         <v>Global Net-zeroHenry Hub2027</v>
       </c>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>13</v>
       </c>
@@ -12470,7 +12471,7 @@
         <v>Global Net-zeroHenry Hub2028</v>
       </c>
     </row>
-    <row r="670" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>13</v>
       </c>
@@ -12488,7 +12489,7 @@
         <v>Global Net-zeroHenry Hub2029</v>
       </c>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>13</v>
       </c>
@@ -12506,7 +12507,7 @@
         <v>Global Net-zeroHenry Hub2030</v>
       </c>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>13</v>
       </c>
@@ -12524,7 +12525,7 @@
         <v>Global Net-zeroHenry Hub2031</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>13</v>
       </c>
@@ -12542,7 +12543,7 @@
         <v>Global Net-zeroHenry Hub2032</v>
       </c>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>13</v>
       </c>
@@ -12560,7 +12561,7 @@
         <v>Global Net-zeroHenry Hub2033</v>
       </c>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>13</v>
       </c>
@@ -12578,7 +12579,7 @@
         <v>Global Net-zeroHenry Hub2034</v>
       </c>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>13</v>
       </c>
@@ -12596,7 +12597,7 @@
         <v>Global Net-zeroHenry Hub2035</v>
       </c>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>13</v>
       </c>
@@ -12614,7 +12615,7 @@
         <v>Global Net-zeroHenry Hub2036</v>
       </c>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>13</v>
       </c>
@@ -12632,7 +12633,7 @@
         <v>Global Net-zeroHenry Hub2037</v>
       </c>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>13</v>
       </c>
@@ -12650,7 +12651,7 @@
         <v>Global Net-zeroHenry Hub2038</v>
       </c>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>13</v>
       </c>
@@ -12668,7 +12669,7 @@
         <v>Global Net-zeroHenry Hub2039</v>
       </c>
     </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>13</v>
       </c>
@@ -12686,7 +12687,7 @@
         <v>Global Net-zeroHenry Hub2040</v>
       </c>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>13</v>
       </c>
@@ -12704,7 +12705,7 @@
         <v>Global Net-zeroHenry Hub2041</v>
       </c>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>13</v>
       </c>
@@ -12722,7 +12723,7 @@
         <v>Global Net-zeroHenry Hub2042</v>
       </c>
     </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>13</v>
       </c>
@@ -12740,7 +12741,7 @@
         <v>Global Net-zeroHenry Hub2043</v>
       </c>
     </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>13</v>
       </c>
@@ -12758,7 +12759,7 @@
         <v>Global Net-zeroHenry Hub2044</v>
       </c>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>13</v>
       </c>
@@ -12776,7 +12777,7 @@
         <v>Global Net-zeroHenry Hub2045</v>
       </c>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>13</v>
       </c>
@@ -12794,7 +12795,7 @@
         <v>Global Net-zeroHenry Hub2046</v>
       </c>
     </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>13</v>
       </c>
@@ -12812,7 +12813,7 @@
         <v>Global Net-zeroHenry Hub2047</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>13</v>
       </c>
@@ -12830,7 +12831,7 @@
         <v>Global Net-zeroHenry Hub2048</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>13</v>
       </c>
@@ -12848,7 +12849,7 @@
         <v>Global Net-zeroHenry Hub2049</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>13</v>
       </c>
@@ -12866,7 +12867,7 @@
         <v>Global Net-zeroHenry Hub2050</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>13</v>
       </c>
@@ -12884,7 +12885,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2005</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>13</v>
       </c>
@@ -12902,7 +12903,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2006</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>13</v>
       </c>
@@ -12920,7 +12921,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2007</v>
       </c>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>13</v>
       </c>
@@ -12938,7 +12939,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2008</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>13</v>
       </c>
@@ -12956,7 +12957,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2009</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>13</v>
       </c>
@@ -12974,7 +12975,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2010</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>13</v>
       </c>
@@ -12992,7 +12993,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2011</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>13</v>
       </c>
@@ -13010,7 +13011,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2012</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>13</v>
       </c>
@@ -13028,7 +13029,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2013</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>13</v>
       </c>
@@ -13046,7 +13047,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2014</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>13</v>
       </c>
@@ -13064,7 +13065,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2015</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>13</v>
       </c>
@@ -13082,7 +13083,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2016</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>13</v>
       </c>
@@ -13100,7 +13101,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2017</v>
       </c>
     </row>
-    <row r="705" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>13</v>
       </c>
@@ -13118,7 +13119,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2018</v>
       </c>
     </row>
-    <row r="706" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>13</v>
       </c>
@@ -13136,7 +13137,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2019</v>
       </c>
     </row>
-    <row r="707" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>13</v>
       </c>
@@ -13154,7 +13155,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2020</v>
       </c>
     </row>
-    <row r="708" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>13</v>
       </c>
@@ -13172,7 +13173,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2021</v>
       </c>
     </row>
-    <row r="709" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>13</v>
       </c>
@@ -13190,7 +13191,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2022</v>
       </c>
     </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>13</v>
       </c>
@@ -13208,7 +13209,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2023</v>
       </c>
     </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>13</v>
       </c>
@@ -13226,7 +13227,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2024</v>
       </c>
     </row>
-    <row r="712" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>13</v>
       </c>
@@ -13244,7 +13245,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2025</v>
       </c>
     </row>
-    <row r="713" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>13</v>
       </c>
@@ -13262,7 +13263,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2026</v>
       </c>
     </row>
-    <row r="714" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>13</v>
       </c>
@@ -13280,7 +13281,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2027</v>
       </c>
     </row>
-    <row r="715" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>13</v>
       </c>
@@ -13298,7 +13299,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2028</v>
       </c>
     </row>
-    <row r="716" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>13</v>
       </c>
@@ -13316,7 +13317,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2029</v>
       </c>
     </row>
-    <row r="717" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>13</v>
       </c>
@@ -13334,7 +13335,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2030</v>
       </c>
     </row>
-    <row r="718" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>13</v>
       </c>
@@ -13352,7 +13353,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2031</v>
       </c>
     </row>
-    <row r="719" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>13</v>
       </c>
@@ -13370,7 +13371,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2032</v>
       </c>
     </row>
-    <row r="720" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>13</v>
       </c>
@@ -13388,7 +13389,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2033</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>13</v>
       </c>
@@ -13406,7 +13407,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2034</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>13</v>
       </c>
@@ -13424,7 +13425,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2035</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>13</v>
       </c>
@@ -13442,7 +13443,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2036</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>13</v>
       </c>
@@ -13460,7 +13461,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2037</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>13</v>
       </c>
@@ -13478,7 +13479,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2038</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>13</v>
       </c>
@@ -13496,7 +13497,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2039</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>13</v>
       </c>
@@ -13514,7 +13515,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2040</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>13</v>
       </c>
@@ -13532,7 +13533,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2041</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>13</v>
       </c>
@@ -13550,7 +13551,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2042</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>13</v>
       </c>
@@ -13568,7 +13569,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2043</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>13</v>
       </c>
@@ -13586,7 +13587,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2044</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>13</v>
       </c>
@@ -13604,7 +13605,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2045</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>13</v>
       </c>
@@ -13622,7 +13623,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2046</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>13</v>
       </c>
@@ -13640,7 +13641,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2047</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>13</v>
       </c>
@@ -13658,7 +13659,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2048</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>13</v>
       </c>
@@ -13676,7 +13677,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2049</v>
       </c>
     </row>
-    <row r="737" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>13</v>
       </c>
@@ -13694,7 +13695,7 @@
         <v>Global Net-zeroNova Inventory Transfer (NIT)2050</v>
       </c>
     </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>13</v>
       </c>
@@ -13712,7 +13713,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2005</v>
       </c>
     </row>
-    <row r="739" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>13</v>
       </c>
@@ -13730,7 +13731,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2006</v>
       </c>
     </row>
-    <row r="740" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>13</v>
       </c>
@@ -13748,7 +13749,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2007</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>13</v>
       </c>
@@ -13766,7 +13767,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2008</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>13</v>
       </c>
@@ -13784,7 +13785,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2009</v>
       </c>
     </row>
-    <row r="743" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>13</v>
       </c>
@@ -13802,7 +13803,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2010</v>
       </c>
     </row>
-    <row r="744" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>13</v>
       </c>
@@ -13820,7 +13821,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2011</v>
       </c>
     </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>13</v>
       </c>
@@ -13838,7 +13839,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2012</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>13</v>
       </c>
@@ -13856,7 +13857,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2013</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>13</v>
       </c>
@@ -13874,7 +13875,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2014</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>13</v>
       </c>
@@ -13892,7 +13893,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2015</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>13</v>
       </c>
@@ -13910,7 +13911,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2016</v>
       </c>
     </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>13</v>
       </c>
@@ -13928,7 +13929,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2017</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>13</v>
       </c>
@@ -13946,7 +13947,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2018</v>
       </c>
     </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>13</v>
       </c>
@@ -13964,7 +13965,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2019</v>
       </c>
     </row>
-    <row r="753" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>13</v>
       </c>
@@ -13982,7 +13983,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2020</v>
       </c>
     </row>
-    <row r="754" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>13</v>
       </c>
@@ -14000,7 +14001,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2021</v>
       </c>
     </row>
-    <row r="755" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>13</v>
       </c>
@@ -14018,7 +14019,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2022</v>
       </c>
     </row>
-    <row r="756" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>13</v>
       </c>
@@ -14036,7 +14037,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2023</v>
       </c>
     </row>
-    <row r="757" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>13</v>
       </c>
@@ -14054,7 +14055,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2024</v>
       </c>
     </row>
-    <row r="758" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>13</v>
       </c>
@@ -14072,7 +14073,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2025</v>
       </c>
     </row>
-    <row r="759" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>13</v>
       </c>
@@ -14090,7 +14091,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2026</v>
       </c>
     </row>
-    <row r="760" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>13</v>
       </c>
@@ -14108,7 +14109,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2027</v>
       </c>
     </row>
-    <row r="761" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>13</v>
       </c>
@@ -14126,7 +14127,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2028</v>
       </c>
     </row>
-    <row r="762" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>13</v>
       </c>
@@ -14144,7 +14145,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2029</v>
       </c>
     </row>
-    <row r="763" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>13</v>
       </c>
@@ -14162,7 +14163,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2030</v>
       </c>
     </row>
-    <row r="764" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>13</v>
       </c>
@@ -14180,7 +14181,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2031</v>
       </c>
     </row>
-    <row r="765" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>13</v>
       </c>
@@ -14198,7 +14199,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2032</v>
       </c>
     </row>
-    <row r="766" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>13</v>
       </c>
@@ -14216,7 +14217,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2033</v>
       </c>
     </row>
-    <row r="767" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>13</v>
       </c>
@@ -14234,7 +14235,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2034</v>
       </c>
     </row>
-    <row r="768" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>13</v>
       </c>
@@ -14252,7 +14253,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2035</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>13</v>
       </c>
@@ -14270,7 +14271,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2036</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>13</v>
       </c>
@@ -14288,7 +14289,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2037</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>13</v>
       </c>
@@ -14306,7 +14307,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2038</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>13</v>
       </c>
@@ -14324,7 +14325,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2039</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>13</v>
       </c>
@@ -14342,7 +14343,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2040</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>13</v>
       </c>
@@ -14360,7 +14361,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2041</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>13</v>
       </c>
@@ -14378,7 +14379,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2042</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>13</v>
       </c>
@@ -14396,7 +14397,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2043</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>13</v>
       </c>
@@ -14414,7 +14415,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2044</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>13</v>
       </c>
@@ -14432,7 +14433,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2045</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>13</v>
       </c>
@@ -14450,7 +14451,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2046</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>13</v>
       </c>
@@ -14468,7 +14469,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2047</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>13</v>
       </c>
@@ -14486,7 +14487,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2048</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>13</v>
       </c>
@@ -14504,7 +14505,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2049</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>13</v>
       </c>
@@ -14522,7 +14523,7 @@
         <v>Global Net-zeroWest Texas Intermediate (WTI)2050</v>
       </c>
     </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>13</v>
       </c>
@@ -14540,7 +14541,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2005</v>
       </c>
     </row>
-    <row r="785" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>13</v>
       </c>
@@ -14558,7 +14559,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2006</v>
       </c>
     </row>
-    <row r="786" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>13</v>
       </c>
@@ -14576,7 +14577,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2007</v>
       </c>
     </row>
-    <row r="787" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>13</v>
       </c>
@@ -14594,7 +14595,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2008</v>
       </c>
     </row>
-    <row r="788" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>13</v>
       </c>
@@ -14612,7 +14613,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2009</v>
       </c>
     </row>
-    <row r="789" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>13</v>
       </c>
@@ -14630,7 +14631,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2010</v>
       </c>
     </row>
-    <row r="790" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>13</v>
       </c>
@@ -14648,7 +14649,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2011</v>
       </c>
     </row>
-    <row r="791" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>13</v>
       </c>
@@ -14666,7 +14667,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2012</v>
       </c>
     </row>
-    <row r="792" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>13</v>
       </c>
@@ -14684,7 +14685,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2013</v>
       </c>
     </row>
-    <row r="793" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>13</v>
       </c>
@@ -14702,7 +14703,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2014</v>
       </c>
     </row>
-    <row r="794" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>13</v>
       </c>
@@ -14720,7 +14721,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2015</v>
       </c>
     </row>
-    <row r="795" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>13</v>
       </c>
@@ -14738,7 +14739,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2016</v>
       </c>
     </row>
-    <row r="796" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>13</v>
       </c>
@@ -14756,7 +14757,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2017</v>
       </c>
     </row>
-    <row r="797" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>13</v>
       </c>
@@ -14774,7 +14775,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2018</v>
       </c>
     </row>
-    <row r="798" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>13</v>
       </c>
@@ -14792,7 +14793,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2019</v>
       </c>
     </row>
-    <row r="799" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>13</v>
       </c>
@@ -14810,7 +14811,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2020</v>
       </c>
     </row>
-    <row r="800" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>13</v>
       </c>
@@ -14828,7 +14829,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2021</v>
       </c>
     </row>
-    <row r="801" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>13</v>
       </c>
@@ -14846,7 +14847,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2022</v>
       </c>
     </row>
-    <row r="802" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>13</v>
       </c>
@@ -14864,7 +14865,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2023</v>
       </c>
     </row>
-    <row r="803" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>13</v>
       </c>
@@ -14882,7 +14883,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2024</v>
       </c>
     </row>
-    <row r="804" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>13</v>
       </c>
@@ -14900,7 +14901,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2025</v>
       </c>
     </row>
-    <row r="805" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>13</v>
       </c>
@@ -14918,7 +14919,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2026</v>
       </c>
     </row>
-    <row r="806" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>13</v>
       </c>
@@ -14936,7 +14937,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2027</v>
       </c>
     </row>
-    <row r="807" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>13</v>
       </c>
@@ -14954,7 +14955,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2028</v>
       </c>
     </row>
-    <row r="808" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>13</v>
       </c>
@@ -14972,7 +14973,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2029</v>
       </c>
     </row>
-    <row r="809" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>13</v>
       </c>
@@ -14990,7 +14991,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2030</v>
       </c>
     </row>
-    <row r="810" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>13</v>
       </c>
@@ -15008,7 +15009,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2031</v>
       </c>
     </row>
-    <row r="811" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>13</v>
       </c>
@@ -15026,7 +15027,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2032</v>
       </c>
     </row>
-    <row r="812" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>13</v>
       </c>
@@ -15044,7 +15045,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2033</v>
       </c>
     </row>
-    <row r="813" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>13</v>
       </c>
@@ -15062,7 +15063,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2034</v>
       </c>
     </row>
-    <row r="814" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>13</v>
       </c>
@@ -15080,7 +15081,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2035</v>
       </c>
     </row>
-    <row r="815" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>13</v>
       </c>
@@ -15098,7 +15099,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2036</v>
       </c>
     </row>
-    <row r="816" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>13</v>
       </c>
@@ -15116,7 +15117,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2037</v>
       </c>
     </row>
-    <row r="817" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>13</v>
       </c>
@@ -15134,7 +15135,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2038</v>
       </c>
     </row>
-    <row r="818" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>13</v>
       </c>
@@ -15152,7 +15153,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2039</v>
       </c>
     </row>
-    <row r="819" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>13</v>
       </c>
@@ -15170,7 +15171,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2040</v>
       </c>
     </row>
-    <row r="820" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>13</v>
       </c>
@@ -15188,7 +15189,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2041</v>
       </c>
     </row>
-    <row r="821" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>13</v>
       </c>
@@ -15206,7 +15207,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2042</v>
       </c>
     </row>
-    <row r="822" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>13</v>
       </c>
@@ -15224,7 +15225,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2043</v>
       </c>
     </row>
-    <row r="823" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>13</v>
       </c>
@@ -15242,7 +15243,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2044</v>
       </c>
     </row>
-    <row r="824" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>13</v>
       </c>
@@ -15260,7 +15261,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2045</v>
       </c>
     </row>
-    <row r="825" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>13</v>
       </c>
@@ -15278,7 +15279,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2046</v>
       </c>
     </row>
-    <row r="826" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>13</v>
       </c>
@@ -15296,7 +15297,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2047</v>
       </c>
     </row>
-    <row r="827" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>13</v>
       </c>
@@ -15314,7 +15315,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2048</v>
       </c>
     </row>
-    <row r="828" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>13</v>
       </c>
@@ -15332,7 +15333,7 @@
         <v>Global Net-zeroWestern Canadian Select (WCS)2049</v>
       </c>
     </row>
-    <row r="829" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>13</v>
       </c>
